--- a/attendance_demo_HR_2026_06_chinh_lai.xlsx
+++ b/attendance_demo_HR_2026_06_chinh_lai.xlsx
@@ -5,40 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\SWP_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\SWP_GROUP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84D7852-BC39-4FE8-AC2F-460059C7E491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EE74AA-4D61-4AA6-964C-B8D9AF08819A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>employeeCode</t>
   </si>
   <si>
+    <t>fullName</t>
+  </si>
+  <si>
     <t>workDate</t>
   </si>
   <si>
@@ -57,6 +46,15 @@
     <t>EMP004</t>
   </si>
   <si>
+    <t>Nguyễn Thị HR</t>
+  </si>
+  <si>
+    <t>Phòng Nhân sự</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
     <t>08:00</t>
   </si>
   <si>
@@ -66,6 +64,9 @@
     <t>PRESENT</t>
   </si>
   <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
     <t>08:10</t>
   </si>
   <si>
@@ -78,64 +79,40 @@
     <t>EMP005</t>
   </si>
   <si>
+    <t>Vũ Thị Nhân Sự</t>
+  </si>
+  <si>
     <t>ABSENT</t>
   </si>
   <si>
     <t>Nghỉ phép năm</t>
   </si>
   <si>
-    <t>Attendance Summary - HR - 06/2026</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Employee</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Late</t>
-  </si>
-  <si>
-    <t>Absent</t>
-  </si>
-  <si>
-    <t>Unexcused</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>UNEXCUSED</t>
+    <t>Department</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
@@ -165,35 +142,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF4C1130"/>
@@ -234,8 +204,11 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -248,45 +221,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Attendance_HR_Table" displayName="Attendance_HR_Table" ref="A1:F5">
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="employeeCode"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="workDate"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="timeIn"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="timeOut"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="attendanceStatus"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Status_HR_Summary" displayName="Status_HR_Summary" ref="A3:B7">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Status"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Count"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Employee_HR_Summary" displayName="Employee_HR_Summary" ref="D3:I5">
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Employee"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Present"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Late"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Absent"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Unexcused"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Total"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ABDCFF9C-E678-479E-B4CF-266188AD75D7}" name="Attendance_HR_Table33" displayName="Attendance_HR_Table33" ref="A1:H5">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{6BC99C56-54B7-4D23-80D1-90EF04757EAF}" name="employeeCode"/>
+    <tableColumn id="7" xr3:uid="{27AABD0D-3063-4FFB-A9B2-817FA36F656E}" name="fullName"/>
+    <tableColumn id="8" xr3:uid="{C7A53E08-B37F-47A2-B882-D94B40FC1622}" name="Department"/>
+    <tableColumn id="2" xr3:uid="{4E1456A0-64C0-48C0-9734-1C94AC89C87D}" name="workDate"/>
+    <tableColumn id="3" xr3:uid="{A6DBBFE5-ED59-43B9-BF22-74602E59715B}" name="timeIn" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{6DBCF681-0CE4-4A7B-9C6A-BCF74D627578}" name="timeOut"/>
+    <tableColumn id="5" xr3:uid="{93825079-1A99-49E2-882F-9F6D0A0C195B}" name="attendanceStatus"/>
+    <tableColumn id="6" xr3:uid="{DF353C0C-1468-46D3-AA48-E98DF566FC84}" name="note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -328,14 +279,72 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -343,15 +352,55 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -360,13 +409,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -400,13 +449,24 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -432,7 +492,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -461,17 +521,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" customWidth="1"/>
+    <col min="4" max="4" width="18.77734375" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="4"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,252 +541,142 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4">
-        <v>46174</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4">
-        <v>46175</v>
-      </c>
-      <c r="C3" s="5" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4">
-        <v>46174</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4">
-        <v>46175</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
+      <c r="G5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E50">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>E2="PRESENT"</formula>
+      <formula>G2="PRESENT"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>E2="LATE"</formula>
+      <formula>G2="LATE"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3">
-      <formula>E2="ABSENT"</formula>
+      <formula>G2="ABSENT"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>E2="UNEXCUSED"</formula>
+      <formula>G2="UNEXCUSED"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E2:E50" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="G2:G5" xr:uid="{74CC875A-DF32-496B-AFC1-CFA0AFEAD680}">
       <formula1>"PRESENT,LATE,ABSENT,UNEXCUSED"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="4" max="9" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="6">
-        <f>COUNTIF(Attendance!$E$2:$E$5,"PRESENT")</f>
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D4,Attendance!$E$2:$E$5,"PRESENT")</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D4,Attendance!$E$2:$E$5,"LATE")</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D4,Attendance!$E$2:$E$5,"ABSENT")</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D4,Attendance!$E$2:$E$5,"UNEXCUSED")</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <f>SUM(E4:H4)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="6">
-        <f>COUNTIF(Attendance!$E$2:$E$5,"LATE")</f>
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D5,Attendance!$E$2:$E$5,"PRESENT")</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D5,Attendance!$E$2:$E$5,"LATE")</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D5,Attendance!$E$2:$E$5,"ABSENT")</f>
-        <v>1</v>
-      </c>
-      <c r="H5" s="6">
-        <f>COUNTIFS(Attendance!$A$2:$A$5,D5,Attendance!$E$2:$E$5,"UNEXCUSED")</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <f>SUM(E5:H5)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="6">
-        <f>COUNTIF(Attendance!$E$2:$E$5,"ABSENT")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="6">
-        <f>COUNTIF(Attendance!$E$2:$E$5,"UNEXCUSED")</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/attendance_demo_HR_2026_06_chinh_lai.xlsx
+++ b/attendance_demo_HR_2026_06_chinh_lai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\SWP_GROUP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EE74AA-4D61-4AA6-964C-B8D9AF08819A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E7519D-4845-4962-9C52-B56219ECB9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
   <si>
     <t>employeeCode</t>
   </si>
@@ -37,12 +37,6 @@
     <t>timeOut</t>
   </si>
   <si>
-    <t>attendanceStatus</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
     <t>EMP004</t>
   </si>
   <si>
@@ -61,34 +55,22 @@
     <t>17:00</t>
   </si>
   <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
     <t>2026-06-02</t>
   </si>
   <si>
     <t>08:10</t>
   </si>
   <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>Kẹt xe</t>
-  </si>
-  <si>
     <t>EMP005</t>
   </si>
   <si>
     <t>Vũ Thị Nhân Sự</t>
   </si>
   <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>Nghỉ phép năm</t>
-  </si>
-  <si>
     <t>Department</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
   </si>
 </sst>
 </file>
@@ -151,59 +133,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF4C1130"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFEADCF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF990000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF274E13"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -221,16 +161,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ABDCFF9C-E678-479E-B4CF-266188AD75D7}" name="Attendance_HR_Table33" displayName="Attendance_HR_Table33" ref="A1:H5">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ABDCFF9C-E678-479E-B4CF-266188AD75D7}" name="Attendance_HR_Table33" displayName="Attendance_HR_Table33" ref="A1:F6">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6BC99C56-54B7-4D23-80D1-90EF04757EAF}" name="employeeCode"/>
     <tableColumn id="7" xr3:uid="{27AABD0D-3063-4FFB-A9B2-817FA36F656E}" name="fullName"/>
     <tableColumn id="8" xr3:uid="{C7A53E08-B37F-47A2-B882-D94B40FC1622}" name="Department"/>
     <tableColumn id="2" xr3:uid="{4E1456A0-64C0-48C0-9734-1C94AC89C87D}" name="workDate"/>
-    <tableColumn id="3" xr3:uid="{A6DBBFE5-ED59-43B9-BF22-74602E59715B}" name="timeIn" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{A6DBBFE5-ED59-43B9-BF22-74602E59715B}" name="timeIn" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{6DBCF681-0CE4-4A7B-9C6A-BCF74D627578}" name="timeOut"/>
-    <tableColumn id="5" xr3:uid="{93825079-1A99-49E2-882F-9F6D0A0C195B}" name="attendanceStatus"/>
-    <tableColumn id="6" xr3:uid="{DF353C0C-1468-46D3-AA48-E98DF566FC84}" name="note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -521,19 +459,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="20.5546875" customWidth="1"/>
     <col min="4" max="4" width="18.77734375" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="4"/>
-    <col min="7" max="7" width="18.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.88671875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +477,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -552,128 +488,100 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
+      <c r="E6" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G5">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>G2="PRESENT"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>G2="LATE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>G2="ABSENT"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>G2="UNEXCUSED"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G5" xr:uid="{74CC875A-DF32-496B-AFC1-CFA0AFEAD680}">
-      <formula1>"PRESENT,LATE,ABSENT,UNEXCUSED"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/attendance_demo_HR_2026_06_chinh_lai.xlsx
+++ b/attendance_demo_HR_2026_06_chinh_lai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\SWP_GROUP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EE74AA-4D61-4AA6-964C-B8D9AF08819A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06592C8B-D33C-4E6D-95E0-675169200281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
   <si>
     <t>employeeCode</t>
   </si>
@@ -37,12 +37,6 @@
     <t>timeOut</t>
   </si>
   <si>
-    <t>attendanceStatus</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
     <t>EMP004</t>
   </si>
   <si>
@@ -61,34 +55,22 @@
     <t>17:00</t>
   </si>
   <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
     <t>2026-06-02</t>
   </si>
   <si>
     <t>08:10</t>
   </si>
   <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>Kẹt xe</t>
-  </si>
-  <si>
     <t>EMP005</t>
   </si>
   <si>
     <t>Vũ Thị Nhân Sự</t>
   </si>
   <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>Nghỉ phép năm</t>
-  </si>
-  <si>
     <t>Department</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
   </si>
 </sst>
 </file>
@@ -151,59 +133,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF4C1130"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFEADCF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF990000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF274E13"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -221,16 +161,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ABDCFF9C-E678-479E-B4CF-266188AD75D7}" name="Attendance_HR_Table33" displayName="Attendance_HR_Table33" ref="A1:H5">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ABDCFF9C-E678-479E-B4CF-266188AD75D7}" name="Attendance_HR_Table33" displayName="Attendance_HR_Table33" ref="A1:F5">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6BC99C56-54B7-4D23-80D1-90EF04757EAF}" name="employeeCode"/>
     <tableColumn id="7" xr3:uid="{27AABD0D-3063-4FFB-A9B2-817FA36F656E}" name="fullName"/>
     <tableColumn id="8" xr3:uid="{C7A53E08-B37F-47A2-B882-D94B40FC1622}" name="Department"/>
     <tableColumn id="2" xr3:uid="{4E1456A0-64C0-48C0-9734-1C94AC89C87D}" name="workDate"/>
-    <tableColumn id="3" xr3:uid="{A6DBBFE5-ED59-43B9-BF22-74602E59715B}" name="timeIn" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{A6DBBFE5-ED59-43B9-BF22-74602E59715B}" name="timeIn" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{6DBCF681-0CE4-4A7B-9C6A-BCF74D627578}" name="timeOut"/>
-    <tableColumn id="5" xr3:uid="{93825079-1A99-49E2-882F-9F6D0A0C195B}" name="attendanceStatus"/>
-    <tableColumn id="6" xr3:uid="{DF353C0C-1468-46D3-AA48-E98DF566FC84}" name="note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -521,19 +459,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="20.5546875" customWidth="1"/>
     <col min="4" max="4" width="18.77734375" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="4"/>
+    <col min="5" max="5" width="8.88671875" style="3"/>
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
     <col min="8" max="8" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +479,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -552,128 +490,99 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G5">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>G2="PRESENT"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>G2="LATE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>G2="ABSENT"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>G2="UNEXCUSED"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G5" xr:uid="{74CC875A-DF32-496B-AFC1-CFA0AFEAD680}">
-      <formula1>"PRESENT,LATE,ABSENT,UNEXCUSED"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
